--- a/proposal/others/21B_Min_collaboration.xlsx
+++ b/proposal/others/21B_Min_collaboration.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A96CEC7-7DD5-4648-B046-E14C887E5AF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13380" yWindow="7680" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -18217,6 +18217,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -18348,22 +18363,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -18379,28 +18403,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7ACA6411-41A0-4B6C-874D-1FC05CC4B568}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>